--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/62.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/62.xlsx
@@ -426,13 +426,13 @@
         <v>-16.93765245774573</v>
       </c>
       <c r="E2">
-        <v>-16.16143295355993</v>
+        <v>-14.49903467381815</v>
       </c>
       <c r="F2">
-        <v>3.822624659713828</v>
+        <v>1.684687916358973</v>
       </c>
       <c r="G2">
-        <v>-12.05037038223818</v>
+        <v>-11.79621024146515</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.23071161380943</v>
       </c>
       <c r="E3">
-        <v>-14.79447684655258</v>
+        <v>-14.7210476405182</v>
       </c>
       <c r="F3">
-        <v>4.111277564893344</v>
+        <v>2.556271246562529</v>
       </c>
       <c r="G3">
-        <v>-11.48695839070905</v>
+        <v>-11.46656231749554</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.44733676368181</v>
       </c>
       <c r="E4">
-        <v>-16.23628862890672</v>
+        <v>-16.64088061064803</v>
       </c>
       <c r="F4">
-        <v>3.941228647711855</v>
+        <v>1.976230167039453</v>
       </c>
       <c r="G4">
-        <v>-10.83043517498755</v>
+        <v>-11.101729854744</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.65917958686018</v>
       </c>
       <c r="E5">
-        <v>-15.76177700848699</v>
+        <v>-17.34225972190402</v>
       </c>
       <c r="F5">
-        <v>3.449711879056352</v>
+        <v>2.652423164475079</v>
       </c>
       <c r="G5">
-        <v>-10.14102099435418</v>
+        <v>-11.05332527429907</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.87418591746471</v>
       </c>
       <c r="E6">
-        <v>-16.18041178812608</v>
+        <v>-17.33161327951199</v>
       </c>
       <c r="F6">
-        <v>3.797957535193264</v>
+        <v>2.211378821672149</v>
       </c>
       <c r="G6">
-        <v>-10.08257587593735</v>
+        <v>-10.14629063617865</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.11715167086487</v>
       </c>
       <c r="E7">
-        <v>-17.40035098647442</v>
+        <v>-18.87541082499289</v>
       </c>
       <c r="F7">
-        <v>3.701345045004758</v>
+        <v>2.371459165528348</v>
       </c>
       <c r="G7">
-        <v>-10.35853645275133</v>
+        <v>-10.45419718609538</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.39858174722249</v>
       </c>
       <c r="E8">
-        <v>-17.32073588494557</v>
+        <v>-18.01010095465922</v>
       </c>
       <c r="F8">
-        <v>3.016374666569069</v>
+        <v>1.858558920736978</v>
       </c>
       <c r="G8">
-        <v>-9.23108575637521</v>
+        <v>-9.31582002192631</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.73497028098977</v>
       </c>
       <c r="E9">
-        <v>-17.57394098061045</v>
+        <v>-18.39555560524411</v>
       </c>
       <c r="F9">
-        <v>3.667935330915048</v>
+        <v>2.125019863195495</v>
       </c>
       <c r="G9">
-        <v>-8.84220850203606</v>
+        <v>-9.775118853374263</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.13455673148182</v>
       </c>
       <c r="E10">
-        <v>-18.39866213841337</v>
+        <v>-19.37067644178977</v>
       </c>
       <c r="F10">
-        <v>3.578259589357585</v>
+        <v>2.207058057299147</v>
       </c>
       <c r="G10">
-        <v>-8.269674714571671</v>
+        <v>-8.451733292797462</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.60269489215953</v>
       </c>
       <c r="E11">
-        <v>-19.74105580240312</v>
+        <v>-19.32871107316069</v>
       </c>
       <c r="F11">
-        <v>3.621062989795041</v>
+        <v>1.805026505698463</v>
       </c>
       <c r="G11">
-        <v>-7.509199118625407</v>
+        <v>-9.478640798149076</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.14122145041028</v>
       </c>
       <c r="E12">
-        <v>-21.93345762305463</v>
+        <v>-19.80530126314994</v>
       </c>
       <c r="F12">
-        <v>3.747274704020379</v>
+        <v>1.992578826101104</v>
       </c>
       <c r="G12">
-        <v>-7.077278799869461</v>
+        <v>-7.67551767703054</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.747463964563252</v>
       </c>
       <c r="E13">
-        <v>-22.66390500896586</v>
+        <v>-22.33853415151475</v>
       </c>
       <c r="F13">
-        <v>3.694964959268396</v>
+        <v>2.582575225071024</v>
       </c>
       <c r="G13">
-        <v>-6.429467227388291</v>
+        <v>-6.010927730151761</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.43107274384819</v>
       </c>
       <c r="E14">
-        <v>-20.98556650071708</v>
+        <v>-21.71129974518633</v>
       </c>
       <c r="F14">
-        <v>3.946755515023334</v>
+        <v>2.626261665159864</v>
       </c>
       <c r="G14">
-        <v>-6.191752569071199</v>
+        <v>-6.658522742010008</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.19581906102556</v>
       </c>
       <c r="E15">
-        <v>-23.35880840239089</v>
+        <v>-23.77943118211935</v>
       </c>
       <c r="F15">
-        <v>3.810661377682598</v>
+        <v>2.854521616470879</v>
       </c>
       <c r="G15">
-        <v>-5.875734839459519</v>
+        <v>-6.341747050218096</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.044454723112551</v>
       </c>
       <c r="E16">
-        <v>-24.1005724448473</v>
+        <v>-24.39153595678813</v>
       </c>
       <c r="F16">
-        <v>4.086380154234802</v>
+        <v>3.061936530457848</v>
       </c>
       <c r="G16">
-        <v>-5.041740193252338</v>
+        <v>-5.215119940453396</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.976219682223464</v>
       </c>
       <c r="E17">
-        <v>-25.10871038538289</v>
+        <v>-25.75984154904978</v>
       </c>
       <c r="F17">
-        <v>4.135876763286878</v>
+        <v>2.946049587541002</v>
       </c>
       <c r="G17">
-        <v>-4.532343671034783</v>
+        <v>-5.773629786972719</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.983885701433575</v>
       </c>
       <c r="E18">
-        <v>-24.70109791147847</v>
+        <v>-27.04218764769782</v>
       </c>
       <c r="F18">
-        <v>4.595179980382314</v>
+        <v>2.874564794149016</v>
       </c>
       <c r="G18">
-        <v>-4.033010655340045</v>
+        <v>-4.916541903430165</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.063038184220719</v>
       </c>
       <c r="E19">
-        <v>-25.811923528612</v>
+        <v>-27.58738874737729</v>
       </c>
       <c r="F19">
-        <v>4.286687675905751</v>
+        <v>2.871557820476854</v>
       </c>
       <c r="G19">
-        <v>-3.994525207669319</v>
+        <v>-4.132103546435276</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.204267889374991</v>
       </c>
       <c r="E20">
-        <v>-27.65197384367468</v>
+        <v>-26.9811302326524</v>
       </c>
       <c r="F20">
-        <v>4.607676731020947</v>
+        <v>3.628402324983845</v>
       </c>
       <c r="G20">
-        <v>-4.120609427312541</v>
+        <v>-4.170923678705067</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.401122192384801</v>
       </c>
       <c r="E21">
-        <v>-27.81641179184121</v>
+        <v>-28.65505800721771</v>
       </c>
       <c r="F21">
-        <v>4.42151938132462</v>
+        <v>2.894591404479097</v>
       </c>
       <c r="G21">
-        <v>-2.787278484189062</v>
+        <v>-4.005845422049402</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.644402269091652</v>
       </c>
       <c r="E22">
-        <v>-28.9530768816625</v>
+        <v>-28.77127676415057</v>
       </c>
       <c r="F22">
-        <v>4.585320751554194</v>
+        <v>3.488191201651195</v>
       </c>
       <c r="G22">
-        <v>-1.877933866090791</v>
+        <v>-3.340777905387113</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.923162670550759</v>
       </c>
       <c r="E23">
-        <v>-29.35285509553365</v>
+        <v>-29.76588588858824</v>
       </c>
       <c r="F23">
-        <v>4.289108165456731</v>
+        <v>4.530797609101931</v>
       </c>
       <c r="G23">
-        <v>-1.830585838988004</v>
+        <v>-4.037328742912274</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.22717540258569</v>
       </c>
       <c r="E24">
-        <v>-29.48953576227016</v>
+        <v>-29.38980744343624</v>
       </c>
       <c r="F24">
-        <v>4.781547735398952</v>
+        <v>3.383372903970557</v>
       </c>
       <c r="G24">
-        <v>-1.347593306659301</v>
+        <v>-2.985831763194181</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.54239217798662</v>
       </c>
       <c r="E25">
-        <v>-29.75745613422296</v>
+        <v>-31.08843577947638</v>
       </c>
       <c r="F25">
-        <v>4.568320995713943</v>
+        <v>3.618006314078711</v>
       </c>
       <c r="G25">
-        <v>-1.282595588788261</v>
+        <v>-2.891893671168838</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.8613494527693</v>
       </c>
       <c r="E26">
-        <v>-29.94251675302042</v>
+        <v>-30.58396603925891</v>
       </c>
       <c r="F26">
-        <v>5.028676239410935</v>
+        <v>4.15455147801559</v>
       </c>
       <c r="G26">
-        <v>-1.376372900957191</v>
+        <v>-1.800982658078694</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.17193328320918</v>
       </c>
       <c r="E27">
-        <v>-30.64078480263315</v>
+        <v>-30.51747671964129</v>
       </c>
       <c r="F27">
-        <v>4.731305595684357</v>
+        <v>4.996376537640976</v>
       </c>
       <c r="G27">
-        <v>-0.3245543615262712</v>
+        <v>-1.840311379690198</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.462272707681</v>
       </c>
       <c r="E28">
-        <v>-31.13861127148137</v>
+        <v>-28.53349565095581</v>
       </c>
       <c r="F28">
-        <v>5.171758484161687</v>
+        <v>4.404471580175007</v>
       </c>
       <c r="G28">
-        <v>-0.003024179694724032</v>
+        <v>-1.789724786908239</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.71858885354079</v>
       </c>
       <c r="E29">
-        <v>-29.75753311828109</v>
+        <v>-31.35596443842753</v>
       </c>
       <c r="F29">
-        <v>4.680553181649636</v>
+        <v>3.688463931891226</v>
       </c>
       <c r="G29">
-        <v>-0.795344030875399</v>
+        <v>-2.231072055204469</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.9309099860277</v>
       </c>
       <c r="E30">
-        <v>-29.81913621444444</v>
+        <v>-30.01926985897643</v>
       </c>
       <c r="F30">
-        <v>4.720560013735242</v>
+        <v>4.206003034138273</v>
       </c>
       <c r="G30">
-        <v>0.1935636475962872</v>
+        <v>-1.956584746870681</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.09305032315493</v>
       </c>
       <c r="E31">
-        <v>-29.7842805500074</v>
+        <v>-29.02829936340391</v>
       </c>
       <c r="F31">
-        <v>4.828113580579924</v>
+        <v>3.879014942292001</v>
       </c>
       <c r="G31">
-        <v>-0.9276888212540422</v>
+        <v>-2.508863553648618</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.20003492840903</v>
       </c>
       <c r="E32">
-        <v>-29.53754437946247</v>
+        <v>-28.8027632439259</v>
       </c>
       <c r="F32">
-        <v>4.468015643643756</v>
+        <v>3.657080404468763</v>
       </c>
       <c r="G32">
-        <v>-1.252834909244097</v>
+        <v>-0.9817830398830477</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.24830180940811</v>
       </c>
       <c r="E33">
-        <v>-30.19971143428606</v>
+        <v>-28.68025443659639</v>
       </c>
       <c r="F33">
-        <v>4.612764563608942</v>
+        <v>3.333369334067967</v>
       </c>
       <c r="G33">
-        <v>-1.589593240333028</v>
+        <v>-0.9630505460001778</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-12.23366895876825</v>
       </c>
       <c r="E34">
-        <v>-28.94318216595574</v>
+        <v>-27.59055867918266</v>
       </c>
       <c r="F34">
-        <v>4.782258474630554</v>
+        <v>4.299139694704633</v>
       </c>
       <c r="G34">
-        <v>-1.104172604050336</v>
+        <v>-1.575500393735212</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-12.15937797224174</v>
       </c>
       <c r="E35">
-        <v>-29.05295237590167</v>
+        <v>-28.44721010721366</v>
       </c>
       <c r="F35">
-        <v>4.593586201499328</v>
+        <v>3.292037114137883</v>
       </c>
       <c r="G35">
-        <v>-0.5543251824479468</v>
+        <v>-1.48416102918495</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-12.03007866652024</v>
       </c>
       <c r="E36">
-        <v>-28.62861171901292</v>
+        <v>-28.39198083821611</v>
       </c>
       <c r="F36">
-        <v>4.729932162530515</v>
+        <v>3.838801018355697</v>
       </c>
       <c r="G36">
-        <v>-1.149341900037652</v>
+        <v>-1.987093544930398</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.85587168734469</v>
       </c>
       <c r="E37">
-        <v>-28.57920606758924</v>
+        <v>-26.98646477503344</v>
       </c>
       <c r="F37">
-        <v>4.467636251373274</v>
+        <v>3.702173412407558</v>
       </c>
       <c r="G37">
-        <v>-2.784164604929149</v>
+        <v>-2.383009019514557</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.64635050170642</v>
       </c>
       <c r="E38">
-        <v>-26.78206304374922</v>
+        <v>-27.01203706775475</v>
       </c>
       <c r="F38">
-        <v>5.080152646555701</v>
+        <v>3.713215549886875</v>
       </c>
       <c r="G38">
-        <v>-1.89283061197067</v>
+        <v>-4.025516345298274</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.41000866023587</v>
       </c>
       <c r="E39">
-        <v>-28.45379903689482</v>
+        <v>-26.27900845165914</v>
       </c>
       <c r="F39">
-        <v>5.174927817844798</v>
+        <v>3.9954502644295</v>
       </c>
       <c r="G39">
-        <v>-2.055083736863652</v>
+        <v>-3.47841530614114</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.15783817708712</v>
       </c>
       <c r="E40">
-        <v>-26.81184681729767</v>
+        <v>-26.31565739180322</v>
       </c>
       <c r="F40">
-        <v>4.933876217099754</v>
+        <v>4.376772630960197</v>
       </c>
       <c r="G40">
-        <v>-3.205509546599004</v>
+        <v>-3.915762765356408</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.89970579527933</v>
       </c>
       <c r="E41">
-        <v>-26.41286108637787</v>
+        <v>-24.96551098031233</v>
       </c>
       <c r="F41">
-        <v>5.276212300185094</v>
+        <v>4.622844138166206</v>
       </c>
       <c r="G41">
-        <v>-3.014450577635658</v>
+        <v>-2.740274985350017</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.6487732673969</v>
       </c>
       <c r="E42">
-        <v>-25.50248384271987</v>
+        <v>-24.51020008968513</v>
       </c>
       <c r="F42">
-        <v>4.911959272356484</v>
+        <v>4.369151650854441</v>
       </c>
       <c r="G42">
-        <v>-2.269806875713714</v>
+        <v>-3.645268703660463</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.41380563873764</v>
       </c>
       <c r="E43">
-        <v>-24.8298197851465</v>
+        <v>-21.43353673497786</v>
       </c>
       <c r="F43">
-        <v>5.5049725854074</v>
+        <v>4.288018033954646</v>
       </c>
       <c r="G43">
-        <v>-2.436023716250505</v>
+        <v>-4.406508824230079</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.20079887107472</v>
       </c>
       <c r="E44">
-        <v>-25.17629785994737</v>
+        <v>-22.3461238739516</v>
       </c>
       <c r="F44">
-        <v>5.362944023993008</v>
+        <v>3.954540511874844</v>
       </c>
       <c r="G44">
-        <v>-3.283458245965173</v>
+        <v>-3.36744439300072</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.01041988295251</v>
       </c>
       <c r="E45">
-        <v>-24.22555379898499</v>
+        <v>-23.69914586643736</v>
       </c>
       <c r="F45">
-        <v>5.522790768241618</v>
+        <v>4.401981507762191</v>
       </c>
       <c r="G45">
-        <v>-3.616531765242847</v>
+        <v>-5.348124256365487</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.84606492447416</v>
       </c>
       <c r="E46">
-        <v>-22.4542230769887</v>
+        <v>-21.83037144074402</v>
       </c>
       <c r="F46">
-        <v>5.923932653251695</v>
+        <v>4.009981485409409</v>
       </c>
       <c r="G46">
-        <v>-3.577311323942804</v>
+        <v>-3.936227744222664</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.708374838464181</v>
       </c>
       <c r="E47">
-        <v>-22.62073959472475</v>
+        <v>-20.99753525751935</v>
       </c>
       <c r="F47">
-        <v>5.935952264266316</v>
+        <v>4.384358819635034</v>
       </c>
       <c r="G47">
-        <v>-4.311327149233706</v>
+        <v>-4.040222780327705</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.59497262442985</v>
       </c>
       <c r="E48">
-        <v>-22.61402839624538</v>
+        <v>-22.63611376398079</v>
       </c>
       <c r="F48">
-        <v>5.654209599960954</v>
+        <v>4.571250102850242</v>
       </c>
       <c r="G48">
-        <v>-4.311504335197916</v>
+        <v>-5.095224104671286</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.50131853706108</v>
       </c>
       <c r="E49">
-        <v>-21.47741311963818</v>
+        <v>-19.70418043855866</v>
       </c>
       <c r="F49">
-        <v>5.893838065507989</v>
+        <v>5.085437630585562</v>
       </c>
       <c r="G49">
-        <v>-5.593845095287624</v>
+        <v>-5.051091674696755</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.418617200686198</v>
       </c>
       <c r="E50">
-        <v>-20.23456437128503</v>
+        <v>-19.38035831921817</v>
       </c>
       <c r="F50">
-        <v>6.359372262207283</v>
+        <v>5.04752656802904</v>
       </c>
       <c r="G50">
-        <v>-4.664773773173971</v>
+        <v>-5.529132843692255</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.344183107672944</v>
       </c>
       <c r="E51">
-        <v>-20.75330106886367</v>
+        <v>-17.90845935555706</v>
       </c>
       <c r="F51">
-        <v>5.869977770837751</v>
+        <v>4.724155128263392</v>
       </c>
       <c r="G51">
-        <v>-3.948988414867345</v>
+        <v>-4.320038792474032</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.273578469510909</v>
       </c>
       <c r="E52">
-        <v>-18.88594405553473</v>
+        <v>-20.33492894071703</v>
       </c>
       <c r="F52">
-        <v>6.083398348495017</v>
+        <v>4.530814176449987</v>
       </c>
       <c r="G52">
-        <v>-5.205948926194748</v>
+        <v>-5.334854996379093</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.205443926344261</v>
       </c>
       <c r="E53">
-        <v>-19.82396310453555</v>
+        <v>-16.23703582711799</v>
       </c>
       <c r="F53">
-        <v>6.038467700567171</v>
+        <v>5.206685767333326</v>
       </c>
       <c r="G53">
-        <v>-5.135524067864386</v>
+        <v>-5.440421737611108</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.138150341604522</v>
       </c>
       <c r="E54">
-        <v>-16.79540572921176</v>
+        <v>-16.3142055526827</v>
       </c>
       <c r="F54">
-        <v>5.922009184142394</v>
+        <v>4.450116280804065</v>
       </c>
       <c r="G54">
-        <v>-5.27560269745864</v>
+        <v>-6.038329211394683</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.069064870196595</v>
       </c>
       <c r="E55">
-        <v>-17.10302496855281</v>
+        <v>-13.93284862558714</v>
       </c>
       <c r="F55">
-        <v>6.711880696999001</v>
+        <v>4.653318118180395</v>
       </c>
       <c r="G55">
-        <v>-4.637992442805784</v>
+        <v>-6.127256878098755</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.999240651458429</v>
       </c>
       <c r="E56">
-        <v>-15.85599191021658</v>
+        <v>-15.42227731213195</v>
       </c>
       <c r="F56">
-        <v>5.94070874989319</v>
+        <v>5.077279868402793</v>
       </c>
       <c r="G56">
-        <v>-6.023580120484979</v>
+        <v>-6.64970281845822</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.928840287305746</v>
       </c>
       <c r="E57">
-        <v>-17.5936307855958</v>
+        <v>-14.96888649448399</v>
       </c>
       <c r="F57">
-        <v>6.619433238111771</v>
+        <v>4.721363530115958</v>
       </c>
       <c r="G57">
-        <v>-5.758759290865315</v>
+        <v>-7.054969774486796</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.862723247653864</v>
       </c>
       <c r="E58">
-        <v>-15.50292037726054</v>
+        <v>-14.07122520583953</v>
       </c>
       <c r="F58">
-        <v>6.146173687013968</v>
+        <v>4.516224969751882</v>
       </c>
       <c r="G58">
-        <v>-5.732128896688862</v>
+        <v>-7.189404702998806</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.803455485600388</v>
       </c>
       <c r="E59">
-        <v>-14.71646482482244</v>
+        <v>-15.22857183645385</v>
       </c>
       <c r="F59">
-        <v>5.935720321393532</v>
+        <v>4.463028871878904</v>
       </c>
       <c r="G59">
-        <v>-6.474541367950383</v>
+        <v>-6.819282911093442</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.753427381579883</v>
       </c>
       <c r="E60">
-        <v>-14.99037410365039</v>
+        <v>-15.45315697639025</v>
       </c>
       <c r="F60">
-        <v>5.895410306838502</v>
+        <v>5.207805720061911</v>
       </c>
       <c r="G60">
-        <v>-5.503122600390537</v>
+        <v>-7.07403695296873</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.71427068611597</v>
       </c>
       <c r="E61">
-        <v>-13.7695790237146</v>
+        <v>-12.19644602361202</v>
       </c>
       <c r="F61">
-        <v>6.188799816827226</v>
+        <v>4.149114074383614</v>
       </c>
       <c r="G61">
-        <v>-5.82449856480879</v>
+        <v>-6.749616014943312</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.688906077597188</v>
       </c>
       <c r="E62">
-        <v>-14.12544462513336</v>
+        <v>-13.73814688562736</v>
       </c>
       <c r="F62">
-        <v>5.876241885137722</v>
+        <v>4.970301188535654</v>
       </c>
       <c r="G62">
-        <v>-5.230515432010311</v>
+        <v>-7.243157674585629</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.682255740988333</v>
       </c>
       <c r="E63">
-        <v>-13.55047786580148</v>
+        <v>-11.99314923998567</v>
       </c>
       <c r="F63">
-        <v>5.737780273759784</v>
+        <v>4.976913217144799</v>
       </c>
       <c r="G63">
-        <v>-6.367845886501919</v>
+        <v>-8.120546475916468</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.696410802459008</v>
       </c>
       <c r="E64">
-        <v>-13.89998548971348</v>
+        <v>-12.00549386013058</v>
       </c>
       <c r="F64">
-        <v>5.582991540872668</v>
+        <v>4.650167008580145</v>
       </c>
       <c r="G64">
-        <v>-6.460697894191085</v>
+        <v>-8.188218389358456</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.73184683843834</v>
       </c>
       <c r="E65">
-        <v>-13.05348237193367</v>
+        <v>-10.96575169949546</v>
       </c>
       <c r="F65">
-        <v>5.45983650236366</v>
+        <v>4.598604451225487</v>
       </c>
       <c r="G65">
-        <v>-6.00130062609635</v>
+        <v>-8.372235856855234</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.784903645733722</v>
       </c>
       <c r="E66">
-        <v>-14.20068522077081</v>
+        <v>-11.99293640170731</v>
       </c>
       <c r="F66">
-        <v>5.645652564690034</v>
+        <v>4.497797108509205</v>
       </c>
       <c r="G66">
-        <v>-6.257016065888555</v>
+        <v>-7.059274737172788</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.855311991190494</v>
       </c>
       <c r="E67">
-        <v>-12.48248708430651</v>
+        <v>-10.44992681070375</v>
       </c>
       <c r="F67">
-        <v>5.210295792474726</v>
+        <v>4.261984103219463</v>
       </c>
       <c r="G67">
-        <v>-6.241253077516983</v>
+        <v>-7.540925249883678</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.940525656292207</v>
       </c>
       <c r="E68">
-        <v>-13.11086266608486</v>
+        <v>-12.12440705909799</v>
       </c>
       <c r="F68">
-        <v>5.510173075962175</v>
+        <v>4.790520611106077</v>
       </c>
       <c r="G68">
-        <v>-6.024971358426184</v>
+        <v>-7.312476761250458</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.039838451228587</v>
       </c>
       <c r="E69">
-        <v>-13.82593135426605</v>
+        <v>-12.42421468077581</v>
       </c>
       <c r="F69">
-        <v>5.447344721929444</v>
+        <v>3.991394577625394</v>
       </c>
       <c r="G69">
-        <v>-5.666363372972912</v>
+        <v>-6.826376912104961</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.150545321333436</v>
       </c>
       <c r="E70">
-        <v>-12.86710396719998</v>
+        <v>-10.35799425987403</v>
       </c>
       <c r="F70">
-        <v>5.260325870134205</v>
+        <v>4.035720517349195</v>
       </c>
       <c r="G70">
-        <v>-5.244080001937055</v>
+        <v>-5.431385253436397</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.268012308174329</v>
       </c>
       <c r="E71">
-        <v>-11.87268730290763</v>
+        <v>-10.1843408671019</v>
       </c>
       <c r="F71">
-        <v>5.251594877708698</v>
+        <v>4.12830217175568</v>
       </c>
       <c r="G71">
-        <v>-4.969773160789036</v>
+        <v>-7.981760647616635</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.389945132953089</v>
       </c>
       <c r="E72">
-        <v>-13.25360922375464</v>
+        <v>-13.06705420853466</v>
       </c>
       <c r="F72">
-        <v>5.153706701719881</v>
+        <v>3.663187128962202</v>
       </c>
       <c r="G72">
-        <v>-4.911964599354739</v>
+        <v>-6.131679964760886</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.511826626848434</v>
       </c>
       <c r="E73">
-        <v>-12.7795640361577</v>
+        <v>-12.29827329014849</v>
       </c>
       <c r="F73">
-        <v>4.5755576133448</v>
+        <v>3.756617031589152</v>
       </c>
       <c r="G73">
-        <v>-5.105966824056908</v>
+        <v>-6.089595017039448</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.634036585783353</v>
       </c>
       <c r="E74">
-        <v>-12.80982782795096</v>
+        <v>-11.0061004029038</v>
       </c>
       <c r="F74">
-        <v>4.607067052612488</v>
+        <v>3.947809198359695</v>
       </c>
       <c r="G74">
-        <v>-4.193295047297361</v>
+        <v>-6.559423288471658</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.753750152168712</v>
       </c>
       <c r="E75">
-        <v>-12.05901589442723</v>
+        <v>-10.82562259980211</v>
       </c>
       <c r="F75">
-        <v>4.643066243203348</v>
+        <v>4.59133801236813</v>
       </c>
       <c r="G75">
-        <v>-4.949334431695255</v>
+        <v>-5.154725776430257</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.86748928538451</v>
       </c>
       <c r="E76">
-        <v>-12.14735736536887</v>
+        <v>-11.2310387638128</v>
       </c>
       <c r="F76">
-        <v>4.693831911116513</v>
+        <v>3.339709658168994</v>
       </c>
       <c r="G76">
-        <v>-4.872271662150137</v>
+        <v>-5.781701592008953</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.971669909137191</v>
       </c>
       <c r="E77">
-        <v>-12.40913033385626</v>
+        <v>-10.9958252953804</v>
       </c>
       <c r="F77">
-        <v>4.420445817170592</v>
+        <v>3.805706083879051</v>
       </c>
       <c r="G77">
-        <v>-4.711898677210717</v>
+        <v>-4.77398267033697</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.06222398888033</v>
       </c>
       <c r="E78">
-        <v>-13.71049149486251</v>
+        <v>-11.17240408236149</v>
       </c>
       <c r="F78">
-        <v>4.017357268763936</v>
+        <v>3.444037562347176</v>
       </c>
       <c r="G78">
-        <v>-5.137053117111088</v>
+        <v>-3.933222145274213</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.14094681267705</v>
       </c>
       <c r="E79">
-        <v>-14.60591118887318</v>
+        <v>-12.61533892626954</v>
       </c>
       <c r="F79">
-        <v>4.073767432159777</v>
+        <v>3.398664566226235</v>
       </c>
       <c r="G79">
-        <v>-3.481630903269396</v>
+        <v>-6.512478851620683</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.20718552477284</v>
       </c>
       <c r="E80">
-        <v>-15.03773741329661</v>
+        <v>-12.91173660701958</v>
       </c>
       <c r="F80">
-        <v>3.719552560518291</v>
+        <v>3.318006432215648</v>
       </c>
       <c r="G80">
-        <v>-2.650723886549651</v>
+        <v>-4.427229738377972</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.26066484787777</v>
       </c>
       <c r="E81">
-        <v>-14.69522628172646</v>
+        <v>-12.00341529056106</v>
       </c>
       <c r="F81">
-        <v>4.328884711404357</v>
+        <v>3.371875164419699</v>
       </c>
       <c r="G81">
-        <v>-3.224537350422224</v>
+        <v>-5.47994077007306</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.29884199993734</v>
       </c>
       <c r="E82">
-        <v>-16.65292182303442</v>
+        <v>-15.01001409542165</v>
       </c>
       <c r="F82">
-        <v>3.947126623619788</v>
+        <v>2.976048084665984</v>
       </c>
       <c r="G82">
-        <v>-2.691269941359709</v>
+        <v>-4.916604246639794</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.32451209874281</v>
       </c>
       <c r="E83">
-        <v>-16.34052957208929</v>
+        <v>-13.84221574679763</v>
       </c>
       <c r="F83">
-        <v>4.23464797892708</v>
+        <v>2.886494941484135</v>
       </c>
       <c r="G83">
-        <v>-1.843159480003796</v>
+        <v>-4.350705089168602</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.34056491364639</v>
       </c>
       <c r="E84">
-        <v>-17.80576262201111</v>
+        <v>-14.86837701388375</v>
       </c>
       <c r="F84">
-        <v>4.062011241979246</v>
+        <v>3.020660639511154</v>
       </c>
       <c r="G84">
-        <v>-3.088881807490101</v>
+        <v>-5.740039921868683</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.35242633383198</v>
       </c>
       <c r="E85">
-        <v>-17.89706571495376</v>
+        <v>-18.01773596183615</v>
       </c>
       <c r="F85">
-        <v>3.975839494535625</v>
+        <v>3.237515628420425</v>
       </c>
       <c r="G85">
-        <v>-2.863002515337927</v>
+        <v>-2.219384344009727</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.36416462801153</v>
       </c>
       <c r="E86">
-        <v>-19.6028920604291</v>
+        <v>-17.11662850447185</v>
       </c>
       <c r="F86">
-        <v>3.788896852541443</v>
+        <v>2.40010576705196</v>
       </c>
       <c r="G86">
-        <v>-2.289563110723131</v>
+        <v>-4.759482952265784</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.37797583820512</v>
       </c>
       <c r="E87">
-        <v>-19.41395959635508</v>
+        <v>-19.21580263072745</v>
       </c>
       <c r="F87">
-        <v>4.086991489378068</v>
+        <v>2.758845181447537</v>
       </c>
       <c r="G87">
-        <v>-2.322526262509312</v>
+        <v>-2.74704742664871</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.39872408296972</v>
       </c>
       <c r="E88">
-        <v>-21.51081061544474</v>
+        <v>-20.00061887557477</v>
       </c>
       <c r="F88">
-        <v>3.341374676648622</v>
+        <v>3.012201351593765</v>
       </c>
       <c r="G88">
-        <v>-2.801919294787304</v>
+        <v>-3.104218237058946</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.42943948149531</v>
       </c>
       <c r="E89">
-        <v>-22.15081531847479</v>
+        <v>-20.47510332515046</v>
       </c>
       <c r="F89">
-        <v>4.036648288840331</v>
+        <v>2.823323643346645</v>
       </c>
       <c r="G89">
-        <v>-1.593209146491535</v>
+        <v>-4.044304619947654</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.47758696438771</v>
       </c>
       <c r="E90">
-        <v>-24.77695437958096</v>
+        <v>-25.18012442048385</v>
       </c>
       <c r="F90">
-        <v>3.491990094560433</v>
+        <v>2.234574765685341</v>
       </c>
       <c r="G90">
-        <v>-2.086875492553112</v>
+        <v>-1.714525751208885</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.54693783034753</v>
       </c>
       <c r="E91">
-        <v>-25.54622437315995</v>
+        <v>-25.05253013684373</v>
       </c>
       <c r="F91">
-        <v>3.238218083977999</v>
+        <v>2.403942764861728</v>
       </c>
       <c r="G91">
-        <v>-2.844932828210065</v>
+        <v>-2.352483815347043</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.64057953297511</v>
       </c>
       <c r="E92">
-        <v>-28.27382842288198</v>
+        <v>-25.34919499756022</v>
       </c>
       <c r="F92">
-        <v>3.196130392976562</v>
+        <v>2.406045161330033</v>
       </c>
       <c r="G92">
-        <v>-1.509787369564213</v>
+        <v>-1.701391021306428</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.76069435214351</v>
       </c>
       <c r="E93">
-        <v>-27.96154485531304</v>
+        <v>-26.51286790636326</v>
       </c>
       <c r="F93">
-        <v>3.256881201563072</v>
+        <v>1.935603716136554</v>
       </c>
       <c r="G93">
-        <v>-1.423514211101733</v>
+        <v>-3.468401017941715</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.90617960588152</v>
       </c>
       <c r="E94">
-        <v>-30.53940359078643</v>
+        <v>-30.30251911544519</v>
       </c>
       <c r="F94">
-        <v>3.191466684498801</v>
+        <v>1.929937683101406</v>
       </c>
       <c r="G94">
-        <v>-2.428093003741327</v>
+        <v>-3.725963785471887</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.08238274201138</v>
       </c>
       <c r="E95">
-        <v>-32.35667341735353</v>
+        <v>-32.27041051598142</v>
       </c>
       <c r="F95">
-        <v>2.777602732916529</v>
+        <v>1.271884275052284</v>
       </c>
       <c r="G95">
-        <v>-2.174769574465957</v>
+        <v>-2.232729072091989</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.29197569982457</v>
       </c>
       <c r="E96">
-        <v>-35.03144828930208</v>
+        <v>-34.18890305780498</v>
       </c>
       <c r="F96">
-        <v>2.441774304147581</v>
+        <v>0.9165825853783256</v>
       </c>
       <c r="G96">
-        <v>-1.711005000475601</v>
+        <v>-4.027406328916514</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.53107462953191</v>
       </c>
       <c r="E97">
-        <v>-37.07374478202134</v>
+        <v>-34.40420256178865</v>
       </c>
       <c r="F97">
-        <v>2.372486341107819</v>
+        <v>1.078006541161865</v>
       </c>
       <c r="G97">
-        <v>-1.489512701548404</v>
+        <v>-3.053707112372854</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.80056820028777</v>
       </c>
       <c r="E98">
-        <v>-39.07262905866606</v>
+        <v>-39.30695494619297</v>
       </c>
       <c r="F98">
-        <v>2.019654843029009</v>
+        <v>0.5998811599400187</v>
       </c>
       <c r="G98">
-        <v>-2.392409719282366</v>
+        <v>-3.974329288970936</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.08905389254269</v>
       </c>
       <c r="E99">
-        <v>-40.83464697386557</v>
+        <v>-40.09476224812236</v>
       </c>
       <c r="F99">
-        <v>1.359841982616341</v>
+        <v>0.9980409223000178</v>
       </c>
       <c r="G99">
-        <v>-1.887606907248034</v>
+        <v>-1.366903295536633</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.40838615740384</v>
       </c>
       <c r="E100">
-        <v>-44.25211422544211</v>
+        <v>-42.89676686155341</v>
       </c>
       <c r="F100">
-        <v>1.670428399887182</v>
+        <v>0.6216166922220748</v>
       </c>
       <c r="G100">
-        <v>-2.461476151887118</v>
+        <v>-4.648964847700567</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.73151394434981</v>
       </c>
       <c r="E101">
-        <v>-46.25213967753676</v>
+        <v>-45.19193334286098</v>
       </c>
       <c r="F101">
-        <v>1.588042291474354</v>
+        <v>0.5504433649735413</v>
       </c>
       <c r="G101">
-        <v>-2.710757116201252</v>
+        <v>-5.679698257390495</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.09372335898802</v>
       </c>
       <c r="E102">
-        <v>-48.23401047733466</v>
+        <v>-47.19209238493886</v>
       </c>
       <c r="F102">
-        <v>1.26699193717135</v>
+        <v>-0.329896637045008</v>
       </c>
       <c r="G102">
-        <v>-2.908161967660565</v>
+        <v>-4.277937438644797</v>
       </c>
     </row>
   </sheetData>
